--- a/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:40</t>
+    <t xml:space="preserve">2026-09-10 00:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:48</t>
+    <t xml:space="preserve">2026-09-18 10:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:58</t>
+    <t xml:space="preserve">2026-09-23 14:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:17</t>
+    <t xml:space="preserve">2026-10-02 15:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:55</t>
+    <t xml:space="preserve">2026-10-04 10:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:00</t>
+    <t xml:space="preserve">2026-10-05 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
